--- a/skyeye-choose-topic/题目信息.xlsx
+++ b/skyeye-choose-topic/题目信息.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\skyeye-choose-topic\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,10 +34,6 @@
   </si>
   <si>
     <t>数据源</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>责任老师</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1561,6 +1557,10 @@
 用户管理：允许用户注册、登录，保存常用路线和设置个人偏好。
 后台管理：管理员可以管理公交线路、车辆信息、站点信息等。
 技术实现：Django框架、数据库、HTML、CSS和JavaScript、地图服务集成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出题教师</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2026,7 +2026,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="25.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2034,16 +2034,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G2" s="4"/>
     </row>
@@ -2052,16 +2052,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -2070,16 +2070,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G4" s="4"/>
       <c r="K4" s="12"/>
@@ -2089,16 +2089,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -2107,16 +2107,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -2125,16 +2125,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -2143,16 +2143,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -2161,16 +2161,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -2179,16 +2179,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -2197,16 +2197,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -2215,16 +2215,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -2233,16 +2233,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -2251,16 +2251,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -2269,16 +2269,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -2287,16 +2287,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -2305,16 +2305,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -2323,16 +2323,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -2341,16 +2341,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -2359,16 +2359,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -2377,16 +2377,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G21" s="4"/>
     </row>
@@ -2395,16 +2395,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G22" s="11"/>
     </row>
@@ -2413,16 +2413,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -2431,16 +2431,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G24" s="4"/>
     </row>
@@ -2449,16 +2449,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -2467,16 +2467,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -2485,16 +2485,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G27" s="4"/>
     </row>
@@ -2503,16 +2503,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G28" s="4"/>
     </row>
@@ -2521,16 +2521,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G29" s="4"/>
     </row>
@@ -2539,16 +2539,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G30" s="4"/>
     </row>
@@ -2557,16 +2557,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G31" s="4"/>
     </row>
@@ -2575,16 +2575,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G32" s="4"/>
     </row>
@@ -2593,16 +2593,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G33" s="4"/>
     </row>
@@ -2611,16 +2611,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G34" s="4"/>
     </row>
@@ -2629,16 +2629,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G35" s="4"/>
     </row>
@@ -2647,16 +2647,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G36" s="4"/>
     </row>
@@ -2665,16 +2665,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G37" s="4"/>
     </row>
@@ -2683,16 +2683,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G38" s="4"/>
     </row>
@@ -2701,16 +2701,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G39" s="4"/>
     </row>
@@ -2719,16 +2719,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G40" s="6"/>
     </row>
@@ -2737,16 +2737,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G41" s="6"/>
     </row>
@@ -2755,16 +2755,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G42" s="6"/>
     </row>
@@ -2773,16 +2773,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G43" s="6"/>
     </row>
@@ -2791,16 +2791,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G44" s="6"/>
     </row>
@@ -2809,16 +2809,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G45" s="6"/>
     </row>
@@ -2827,16 +2827,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G46" s="6"/>
     </row>
@@ -2845,16 +2845,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G47" s="6"/>
     </row>
@@ -2863,16 +2863,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G48" s="6"/>
     </row>
@@ -2881,16 +2881,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G49" s="5"/>
     </row>
@@ -2899,16 +2899,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G50" s="6"/>
     </row>
@@ -2917,16 +2917,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G51" s="6"/>
     </row>
@@ -2935,16 +2935,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G52" s="6"/>
     </row>
@@ -2953,16 +2953,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G53" s="6"/>
     </row>
@@ -2971,16 +2971,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G54" s="6"/>
     </row>
@@ -2989,16 +2989,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G55" s="6"/>
     </row>
@@ -3007,16 +3007,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G56" s="6"/>
     </row>
@@ -3025,16 +3025,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G57" s="6"/>
     </row>
@@ -3043,16 +3043,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G58" s="6"/>
     </row>
@@ -3061,16 +3061,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G59" s="6"/>
     </row>
@@ -3079,16 +3079,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G60" s="6"/>
     </row>
@@ -3097,16 +3097,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G61" s="6"/>
     </row>
@@ -3115,16 +3115,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G62" s="6"/>
     </row>
@@ -3133,16 +3133,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G63" s="6"/>
     </row>
@@ -3151,16 +3151,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G64" s="6"/>
     </row>
@@ -3169,16 +3169,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G65" s="6"/>
     </row>
@@ -3187,16 +3187,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G66" s="6"/>
     </row>
@@ -3205,16 +3205,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G67" s="6"/>
     </row>
@@ -3223,16 +3223,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G68" s="6"/>
     </row>
@@ -3241,16 +3241,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G69" s="6"/>
     </row>
@@ -3259,16 +3259,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G70" s="6"/>
     </row>
@@ -3277,16 +3277,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G71" s="6"/>
     </row>
@@ -3295,16 +3295,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G72" s="6"/>
     </row>
@@ -3313,16 +3313,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G73" s="6"/>
     </row>
@@ -3331,16 +3331,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G74" s="6"/>
     </row>
@@ -3349,16 +3349,16 @@
         <v>74</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G75" s="6"/>
     </row>
@@ -3367,16 +3367,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G76" s="6"/>
     </row>
@@ -3385,16 +3385,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G77" s="6"/>
     </row>
@@ -3403,16 +3403,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G78" s="6"/>
     </row>
@@ -3421,16 +3421,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G79" s="6"/>
     </row>
@@ -3439,16 +3439,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G80" s="6"/>
     </row>
@@ -3457,16 +3457,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G81" s="6"/>
     </row>
@@ -3475,16 +3475,16 @@
         <v>81</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G82" s="6"/>
     </row>
@@ -3493,16 +3493,16 @@
         <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G83" s="6"/>
     </row>
@@ -3511,14 +3511,14 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3526,14 +3526,14 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C85" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3541,14 +3541,14 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C86" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3556,14 +3556,14 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C87" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3571,14 +3571,14 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C88" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3586,14 +3586,14 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>97</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3601,14 +3601,14 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>99</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3616,14 +3616,14 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C91" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>101</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3631,14 +3631,14 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C92" s="7" t="s">
         <v>102</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>103</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3646,14 +3646,14 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C93" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3661,14 +3661,14 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C94" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>107</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3676,14 +3676,14 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C95" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>109</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3691,14 +3691,14 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C96" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3706,14 +3706,14 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C97" s="7" t="s">
         <v>112</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>113</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3721,14 +3721,14 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C98" s="7" t="s">
         <v>114</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>115</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3736,14 +3736,14 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C99" s="7" t="s">
         <v>116</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>117</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3751,14 +3751,14 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C100" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3766,14 +3766,14 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C101" s="7" t="s">
         <v>120</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>121</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3781,14 +3781,14 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C102" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>123</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3796,14 +3796,14 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C103" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>125</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3811,14 +3811,14 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C104" s="7" t="s">
         <v>126</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>127</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3826,14 +3826,14 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C105" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3841,14 +3841,14 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C106" s="7" t="s">
         <v>130</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>131</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3856,14 +3856,14 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C107" s="7" t="s">
         <v>132</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>133</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3871,14 +3871,14 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C108" s="7" t="s">
         <v>134</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>135</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3886,14 +3886,14 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C109" s="7" t="s">
         <v>136</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>137</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3901,14 +3901,14 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C110" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>139</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3916,14 +3916,14 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C111" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>141</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3931,14 +3931,14 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C112" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>143</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3946,14 +3946,14 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C113" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3961,14 +3961,14 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C114" s="7" t="s">
         <v>146</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>147</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3976,14 +3976,14 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C115" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>149</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -3991,14 +3991,14 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C116" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -4006,14 +4006,14 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C117" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -4021,14 +4021,14 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C118" s="7" t="s">
         <v>154</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>155</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -4036,14 +4036,14 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C119" s="7" t="s">
         <v>156</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>157</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -4051,14 +4051,14 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C120" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>159</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -4066,14 +4066,14 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C121" s="7" t="s">
         <v>160</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>161</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -4081,14 +4081,14 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C122" s="7" t="s">
         <v>162</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>163</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -4096,14 +4096,14 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C123" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>165</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
